--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.69476858351799</v>
+        <v>7.262899894821674</v>
       </c>
       <c r="D2" t="n">
-        <v>44.78749559425114</v>
+        <v>7.27796803406581</v>
       </c>
       <c r="E2" t="n">
-        <v>11.65123921489777</v>
+        <v>1.893326372420887</v>
       </c>
       <c r="F2" t="n">
-        <v>11.97803178893344</v>
+        <v>1.946430165701684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.57141003214835</v>
+        <v>4.317854130224108</v>
       </c>
       <c r="D3" t="n">
-        <v>27.22697771475822</v>
+        <v>4.424383878648212</v>
       </c>
       <c r="E3" t="n">
-        <v>11.65123921489777</v>
+        <v>1.893326372420887</v>
       </c>
       <c r="F3" t="n">
-        <v>11.97803178893344</v>
+        <v>1.946430165701684</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.86743904801267</v>
+        <v>2.090958845302058</v>
       </c>
       <c r="D4" t="n">
-        <v>12.07434119673492</v>
+        <v>1.962080444469424</v>
       </c>
       <c r="E4" t="n">
-        <v>11.65123921489777</v>
+        <v>1.893326372420887</v>
       </c>
       <c r="F4" t="n">
-        <v>11.97803178893344</v>
+        <v>1.946430165701684</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.70395700145217</v>
+        <v>5.639393012735979</v>
       </c>
       <c r="D5" t="n">
-        <v>35.13372865052738</v>
+        <v>5.7092309057107</v>
       </c>
       <c r="E5" t="n">
-        <v>11.65123921489777</v>
+        <v>1.893326372420887</v>
       </c>
       <c r="F5" t="n">
-        <v>11.97803178893344</v>
+        <v>1.946430165701684</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
